--- a/content/post/drafts/season-prediction/ladies_model-exhaustive-tests-predicted_rmse.xlsx
+++ b/content/post/drafts/season-prediction/ladies_model-exhaustive-tests-predicted_rmse.xlsx
@@ -483,25 +483,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.155758572081031</v>
+        <v>0.157446267454112</v>
       </c>
       <c r="C4" t="n">
-        <v>0.15354484238244</v>
+        <v>0.155689205375843</v>
       </c>
       <c r="D4" t="n">
-        <v>0.231922031933629</v>
+        <v>0.232682475367958</v>
       </c>
       <c r="E4" t="n">
-        <v>0.262442126862313</v>
+        <v>0.267582347027772</v>
       </c>
       <c r="F4" t="n">
-        <v>0.139803611492852</v>
+        <v>0.137184489651463</v>
       </c>
       <c r="G4" t="n">
-        <v>0.155505478265207</v>
+        <v>0.153676989514009</v>
       </c>
       <c r="H4" t="n">
-        <v>0.183162777169579</v>
+        <v>0.184043629065193</v>
       </c>
     </row>
     <row r="5">
